--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajmond\Desktop\Programozás\Inventory _M_S\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajmond\Desktop\Programozás\inventory-checker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D595D0-A30B-4268-B25E-CFEC5A624558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8F465D-637C-4D1B-9AA2-19E971776A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7455" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>rubber band</t>
   </si>
@@ -132,19 +132,16 @@
     <t>credit card</t>
   </si>
   <si>
-    <t>Cikkszám</t>
-  </si>
-  <si>
-    <t>Megnevezés</t>
-  </si>
-  <si>
-    <t>Minimum (db)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Készlet </t>
-  </si>
-  <si>
-    <t>db</t>
+    <t>Item number</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Minimum</t>
   </si>
 </sst>
 </file>
@@ -522,17 +519,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -540,14 +534,13 @@
         <v>36</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>11442</v>
       </c>
@@ -557,14 +550,11 @@
       <c r="C2">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>11443</v>
       </c>
@@ -574,14 +564,11 @@
       <c r="C3">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>11444</v>
       </c>
@@ -591,14 +578,11 @@
       <c r="C4">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>11445</v>
       </c>
@@ -608,14 +592,11 @@
       <c r="C5">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5">
+      <c r="D5">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>11446</v>
       </c>
@@ -625,14 +606,11 @@
       <c r="C6">
         <v>5456</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>11447</v>
       </c>
@@ -642,14 +620,11 @@
       <c r="C7">
         <v>352</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>11448</v>
       </c>
@@ -659,14 +634,11 @@
       <c r="C8">
         <v>532</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>11449</v>
       </c>
@@ -676,14 +648,11 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>11450</v>
       </c>
@@ -693,14 +662,11 @@
       <c r="C10">
         <v>855</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10">
+      <c r="D10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>11451</v>
       </c>
@@ -710,14 +676,11 @@
       <c r="C11">
         <v>45</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11452</v>
       </c>
@@ -727,14 +690,11 @@
       <c r="C12">
         <v>22</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11453</v>
       </c>
@@ -744,14 +704,11 @@
       <c r="C13">
         <v>556</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11454</v>
       </c>
@@ -761,14 +718,11 @@
       <c r="C14">
         <v>55</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14">
+      <c r="D14">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>11455</v>
       </c>
@@ -778,14 +732,11 @@
       <c r="C15">
         <v>88</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>11456</v>
       </c>
@@ -795,14 +746,11 @@
       <c r="C16">
         <v>55</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>11457</v>
       </c>
@@ -812,14 +760,11 @@
       <c r="C17">
         <v>55</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>11458</v>
       </c>
@@ -829,14 +774,11 @@
       <c r="C18">
         <v>255</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>11459</v>
       </c>
@@ -846,14 +788,11 @@
       <c r="C19">
         <v>55</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19">
+      <c r="D19">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>11460</v>
       </c>
@@ -863,14 +802,11 @@
       <c r="C20">
         <v>2</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>11461</v>
       </c>
@@ -880,14 +816,11 @@
       <c r="C21">
         <v>5</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>11462</v>
       </c>
@@ -897,14 +830,11 @@
       <c r="C22">
         <v>55</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>11463</v>
       </c>
@@ -914,14 +844,11 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>11464</v>
       </c>
@@ -931,14 +858,11 @@
       <c r="C24">
         <v>44</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24">
+      <c r="D24">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>11465</v>
       </c>
@@ -948,14 +872,11 @@
       <c r="C25">
         <v>5</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>11466</v>
       </c>
@@ -965,14 +886,11 @@
       <c r="C26">
         <v>55</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>11467</v>
       </c>
@@ -982,14 +900,11 @@
       <c r="C27">
         <v>5</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27">
+      <c r="D27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>11468</v>
       </c>
@@ -999,14 +914,11 @@
       <c r="C28">
         <v>5</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>11469</v>
       </c>
@@ -1016,14 +928,11 @@
       <c r="C29">
         <v>5</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>11470</v>
       </c>
@@ -1033,14 +942,11 @@
       <c r="C30">
         <v>5</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>11471</v>
       </c>
@@ -1050,14 +956,11 @@
       <c r="C31">
         <v>5</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31">
+      <c r="D31">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>11472</v>
       </c>
@@ -1067,14 +970,11 @@
       <c r="C32">
         <v>556</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>11473</v>
       </c>
@@ -1084,14 +984,11 @@
       <c r="C33">
         <v>56</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>11474</v>
       </c>
@@ -1101,14 +998,11 @@
       <c r="C34">
         <v>66</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>11475</v>
       </c>
@@ -1118,14 +1012,11 @@
       <c r="C35">
         <v>5</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>11476</v>
       </c>
@@ -1135,14 +1026,11 @@
       <c r="C36">
         <v>56</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>11477</v>
       </c>
@@ -1152,460 +1040,371 @@
       <c r="C37">
         <v>456</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E37">
+      <c r="D37">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
-      <c r="D56" s="3"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
-      <c r="D57" s="3"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
-      <c r="D58" s="3"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
-      <c r="D59" s="3"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
-      <c r="D60" s="3"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
-      <c r="D62" s="3"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
-      <c r="D63" s="3"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
-      <c r="D64" s="3"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
-      <c r="D65" s="3"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
-      <c r="D66" s="3"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
-      <c r="D67" s="3"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
-      <c r="D68" s="3"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
-      <c r="D69" s="3"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
-      <c r="D70" s="3"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
-      <c r="D71" s="3"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
-      <c r="D72" s="3"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
-      <c r="D73" s="3"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
-      <c r="D74" s="3"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
-      <c r="D75" s="3"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
-      <c r="D76" s="3"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
-      <c r="D77" s="3"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
-      <c r="D78" s="3"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
-      <c r="D79" s="3"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
-      <c r="D80" s="3"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
-      <c r="D81" s="3"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
-      <c r="D82" s="3"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
-      <c r="D83" s="3"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
-      <c r="D84" s="3"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
-      <c r="D86" s="3"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
-      <c r="D87" s="3"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
-      <c r="D88" s="3"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
-      <c r="D89" s="3"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
-      <c r="D90" s="3"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
-      <c r="D91" s="3"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
-      <c r="D92" s="3"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
-      <c r="D93" s="3"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
-      <c r="D94" s="3"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
-      <c r="D96" s="3"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
-      <c r="D97" s="3"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
-      <c r="D98" s="3"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
-      <c r="D99" s="3"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
-      <c r="D100" s="3"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
-      <c r="D101" s="3"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
-      <c r="D102" s="3"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
-      <c r="D103" s="3"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
-      <c r="D104" s="3"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
-      <c r="D105" s="3"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
-      <c r="D106" s="3"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
-      <c r="D107" s="3"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
-      <c r="D108" s="3"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
-      <c r="D109" s="3"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
-      <c r="D110" s="3"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
-      <c r="D111" s="3"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
-      <c r="D112" s="3"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
-      <c r="D113" s="3"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
-      <c r="D114" s="3"/>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
-      <c r="D115" s="3"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
-      <c r="D116" s="3"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
-      <c r="D117" s="3"/>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
-      <c r="D118" s="3"/>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
-      <c r="D119" s="3"/>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
-      <c r="D120" s="3"/>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
-      <c r="D121" s="3"/>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
-      <c r="D122" s="3"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
-      <c r="D123" s="3"/>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
     </row>
